--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,10 +426,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
@@ -549,6 +549,43 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>labubu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>****9012</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10.00%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-10-22 09:22:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -586,6 +586,43 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>daulat</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>****9012</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-10-22 09:30:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -623,6 +623,43 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>****8912</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-10-22 09:49:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -660,6 +660,43 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Arshae</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>****9012</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-10-22 09:59:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,80 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>****9012</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-10-22 10:26:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Emon</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>012345</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50.00%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-10-22 10:29:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,10 +426,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
@@ -586,6 +586,117 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>****9012</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>70.00%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-10-22 10:43:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ayon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>****9012</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>70.00%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-10-22 10:46:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kaji the paji</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>****test</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-10-22 10:52:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,43 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>****9012</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0/10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-10-22 11:18:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,10 +426,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
@@ -512,6 +512,43 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Player-123456</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>****3456</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0/10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-10-29 04:52:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -549,6 +549,43 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Player-123456</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>****3456</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0/10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-10-29 04:59:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -586,6 +586,43 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Player-123456</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>****3456</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>40.00%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-10-29 05:07:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,43 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Player-123456</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>****3456</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-10-29 05:50:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quiz_results.xlsx
+++ b/quiz_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -549,6 +549,43 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Player-123456</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>****3456</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>80.00%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-10-29 05:58:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
